--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0003T0006Z000C1N41_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0003T0006Z000C1N41_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.37008445384762</v>
+        <v>6.722638723750238</v>
       </c>
       <c r="D2" t="n">
-        <v>41.18964792538637</v>
+        <v>6.693317787875286</v>
       </c>
       <c r="E2" t="n">
-        <v>11.1373743321297</v>
+        <v>1.809823328971076</v>
       </c>
       <c r="F2" t="n">
-        <v>11.16913904832063</v>
+        <v>1.814985095352103</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>35.21208671598535</v>
+        <v>5.72196409134762</v>
       </c>
       <c r="D3" t="n">
-        <v>35.2814099897831</v>
+        <v>5.733229123339754</v>
       </c>
       <c r="E3" t="n">
-        <v>11.1373743321297</v>
+        <v>1.809823328971076</v>
       </c>
       <c r="F3" t="n">
-        <v>11.16913904832063</v>
+        <v>1.814985095352103</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.26911758110386</v>
+        <v>6.218731606929378</v>
       </c>
       <c r="D4" t="n">
-        <v>38.42280766249939</v>
+        <v>6.243706245156151</v>
       </c>
       <c r="E4" t="n">
-        <v>11.1373743321297</v>
+        <v>1.809823328971076</v>
       </c>
       <c r="F4" t="n">
-        <v>11.16913904832063</v>
+        <v>1.814985095352103</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>6.507849069436887</v>
+        <v>1.057525473783494</v>
       </c>
       <c r="D5" t="n">
-        <v>6.522072569334163</v>
+        <v>1.059836792516802</v>
       </c>
       <c r="E5" t="n">
-        <v>11.1373743321297</v>
+        <v>1.809823328971076</v>
       </c>
       <c r="F5" t="n">
-        <v>11.16913904832063</v>
+        <v>1.814985095352103</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>27.43993386286054</v>
+        <v>4.458989252714837</v>
       </c>
       <c r="D6" t="n">
-        <v>27.26754199025401</v>
+        <v>4.430975573416276</v>
       </c>
       <c r="E6" t="n">
-        <v>11.1373743321297</v>
+        <v>1.809823328971076</v>
       </c>
       <c r="F6" t="n">
-        <v>11.16913904832063</v>
+        <v>1.814985095352103</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.34279763295244</v>
+        <v>4.930704615354772</v>
       </c>
       <c r="D7" t="n">
-        <v>30.54777237856392</v>
+        <v>4.964013011516638</v>
       </c>
       <c r="E7" t="n">
-        <v>11.1373743321297</v>
+        <v>1.809823328971076</v>
       </c>
       <c r="F7" t="n">
-        <v>11.16913904832063</v>
+        <v>1.814985095352103</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>45.21433713129928</v>
+        <v>7.347329783836133</v>
       </c>
       <c r="D8" t="n">
-        <v>45.4524412423072</v>
+        <v>7.386021701874919</v>
       </c>
       <c r="E8" t="n">
-        <v>11.1373743321297</v>
+        <v>1.809823328971076</v>
       </c>
       <c r="F8" t="n">
-        <v>11.16913904832063</v>
+        <v>1.814985095352103</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>34.86314054054028</v>
+        <v>5.665260337837796</v>
       </c>
       <c r="D9" t="n">
-        <v>34.92534786351443</v>
+        <v>5.675369027821096</v>
       </c>
       <c r="E9" t="n">
-        <v>11.1373743321297</v>
+        <v>1.809823328971076</v>
       </c>
       <c r="F9" t="n">
-        <v>11.16913904832063</v>
+        <v>1.814985095352103</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
